--- a/products/IZ381H/IZ381H - PO#20164777 - 20250304.xlsx
+++ b/products/IZ381H/IZ381H - PO#20164777 - 20250304.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zoe/Desktop/Code Battery/code PO/IZ381H - PO#20164777 - 20250304/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAAFF13-9BA7-294C-BEFB-8800B46323C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22192" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Data record" sheetId="2" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="______Huifang_Ma，Dike">#REF!</definedName>
+    <definedName name="_______Huifang_Ma，Dike">#REF!</definedName>
     <definedName name="Appearance" localSheetId="0">#REF!</definedName>
     <definedName name="Assembly" localSheetId="0">#REF!</definedName>
     <definedName name="DCC">#REF!</definedName>
@@ -78,7 +72,7 @@
         <b/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Inspected By: </t>
     </r>
@@ -86,7 +80,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Ngọc Hà / Minh Trung</t>
     </r>
@@ -97,7 +91,7 @@
         <b/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Date:</t>
     </r>
@@ -105,7 +99,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 2025.03.04</t>
     </r>
@@ -118,7 +112,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Barcode # 
 </t>
@@ -127,6 +121,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
       </rPr>
       <t>二维码</t>
     </r>
@@ -175,7 +170,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">Whole machine BOOST Mode, Carpet, Air Watts </t>
     </r>
@@ -183,6 +178,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
       </rPr>
       <t>（</t>
     </r>
@@ -190,7 +186,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>End of Nozzle) (AW)</t>
     </r>
@@ -265,13 +261,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="169" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="170" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="7">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,7 +282,7 @@
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,116 +294,253 @@
       <b/>
       <sz val="18"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="24"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="18"/>
       <name val="細明體"/>
-      <family val="1"/>
       <charset val="136"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,8 +571,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -767,404 +1090,577 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="52"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="52" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="52" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="7" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="8" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="9" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="6" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="13" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="2" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="2" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="2" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="2" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="5" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="5" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="14" fillId="3" borderId="5" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="3" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="13" fillId="3" borderId="5" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="18" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="16" fillId="5" borderId="5" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="5" borderId="5" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="51" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="51" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="51" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="26" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="51" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="一般_吸塵器測試數據表 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="一般_吸塵器測試數據表 2 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="49"/>
+    <cellStyle name="一般_吸塵器測試數據表 2 2" xfId="50"/>
+    <cellStyle name="一般_吸塵器測試數據表 2 2 2" xfId="51"/>
+    <cellStyle name="常规 2" xfId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1175,7 +1671,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1203,120 +1699,161 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>56029</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>221129</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>197859</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="55880" y="44450"/>
-          <a:ext cx="2305050" cy="438785"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="CL1264 SK410 database  "/>
@@ -1343,7 +1880,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="CL1270 SK435  "/>
@@ -1623,746 +2160,737 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.3362831858407" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16.6637168141593" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5044247787611" style="2" customWidth="1"/>
     <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="31.1640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11.6637168141593" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.6637168141593" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.1681415929204" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.8318584070796" style="3" customWidth="1"/>
+    <col min="8" max="8" width="31.1681415929204" style="4" customWidth="1"/>
     <col min="9" max="9" width="11" style="4" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="10.33203125" style="2"/>
+    <col min="11" max="16384" width="10.3362831858407" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.5" customHeight="1">
+    <row r="1" ht="22.5" customHeight="1" spans="1:10">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-    </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:10">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:10">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="12">
         <v>20164777</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="71" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="72"/>
-      <c r="I3" s="36" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="J3" s="64"/>
+    </row>
+    <row r="4" ht="61.5" customHeight="1" spans="1:10">
+      <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="56" t="s">
+      <c r="E4" s="19"/>
+      <c r="F4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="G4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="52" t="s">
+      <c r="J4" s="17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A5" s="46" t="s">
+    <row r="5" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="56" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="63" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="59.25" customHeight="1">
-      <c r="A6" s="47"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="64"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" ht="59.25" customHeight="1" spans="1:10">
+      <c r="A6" s="25"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
       <c r="I6" s="65"/>
       <c r="J6" s="65"/>
     </row>
-    <row r="7" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A7" s="48" t="s">
+    <row r="7" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="54" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="31" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="68" t="s">
+      <c r="J7" s="67" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="49"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="67"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="69"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A9" s="11">
+    <row r="9" s="1" customFormat="1" spans="1:10">
+      <c r="A9" s="38">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="41">
         <v>89.42</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="42">
         <v>23.44</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="41">
         <v>1315</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="42">
         <v>2362</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="41">
         <v>34.64</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A10" s="11">
+    <row r="10" s="1" customFormat="1" spans="1:10">
+      <c r="A10" s="38">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="41">
         <v>87.83</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="42">
         <v>24.19</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="41">
         <v>1305</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="42">
         <v>2523</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="41">
         <v>32.18</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A11" s="11">
+    <row r="11" s="1" customFormat="1" spans="1:10">
+      <c r="A11" s="38">
         <v>3</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="41">
         <v>87.09</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="42">
         <v>23.75</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="41">
         <v>1326</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="42">
         <v>2402</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="41">
         <v>33.92</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A12" s="11">
+    <row r="12" s="1" customFormat="1" spans="1:10">
+      <c r="A12" s="38">
         <v>4</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="41">
         <v>88.23</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="42">
         <v>23.96</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="41">
         <v>1291</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="42">
         <v>2580</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="41">
         <v>34.6</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A13" s="11">
+    <row r="13" s="1" customFormat="1" spans="1:10">
+      <c r="A13" s="38">
         <v>5</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="41">
         <v>87.16</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="42">
         <v>27.49</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="41">
         <v>1329</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="42">
         <v>2338</v>
       </c>
-      <c r="H13" s="14">
-        <v>34.270000000000003</v>
-      </c>
-      <c r="I13" s="12" t="s">
+      <c r="H13" s="41">
+        <v>34.27</v>
+      </c>
+      <c r="I13" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A14" s="11">
+    <row r="14" s="1" customFormat="1" spans="1:10">
+      <c r="A14" s="38">
         <v>6</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A15" s="11">
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:10">
+      <c r="A15" s="38">
         <v>7</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="38"/>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A16" s="11">
+      <c r="B15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="70"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:10">
+      <c r="A16" s="38">
         <v>8</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="38"/>
-    </row>
-    <row r="17" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A17" s="11">
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="70"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:10">
+      <c r="A17" s="38">
         <v>9</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="38"/>
-    </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A18" s="11">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="70"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:10">
+      <c r="A18" s="38">
         <v>10</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="38"/>
-    </row>
-    <row r="19" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A19" s="11">
+      <c r="B18" s="43"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="70"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:10">
+      <c r="A19" s="38">
         <v>11</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="38"/>
-    </row>
-    <row r="20" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A20" s="11">
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="70"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:10">
+      <c r="A20" s="38">
         <v>12</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A21" s="11">
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="70"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:10">
+      <c r="A21" s="38">
         <v>13</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="38"/>
-    </row>
-    <row r="22" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A22" s="11">
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="70"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:10">
+      <c r="A22" s="38">
         <v>14</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="38"/>
-    </row>
-    <row r="23" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A23" s="11">
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="70"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:10">
+      <c r="A23" s="38">
         <v>15</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="38"/>
-    </row>
-    <row r="24" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A24" s="11">
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="70"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:10">
+      <c r="A24" s="38">
         <v>16</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="38"/>
-    </row>
-    <row r="25" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A25" s="11">
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="70"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:10">
+      <c r="A25" s="38">
         <v>17</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="38"/>
-    </row>
-    <row r="26" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A26" s="11">
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="70"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:10">
+      <c r="A26" s="38">
         <v>18</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="38"/>
-    </row>
-    <row r="27" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A27" s="11">
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="70"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:10">
+      <c r="A27" s="38">
         <v>19</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="38"/>
-    </row>
-    <row r="28" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A28" s="11">
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="70"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:10">
+      <c r="A28" s="38">
         <v>20</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="38"/>
-    </row>
-    <row r="29" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A29" s="23" t="s">
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="70"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:10">
+      <c r="A29" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="25" t="str">
+      <c r="B29" s="51"/>
+      <c r="C29" s="52" t="str">
         <f t="shared" ref="C29:J29" si="0">IF(C9=" "," ",IF(MIN(C9:C28)=0," ",MIN(C9:C28)))</f>
         <v/>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="52">
         <f t="shared" si="0"/>
         <v>87.09</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="52">
         <f t="shared" si="0"/>
         <v>23.44</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="53">
         <f t="shared" si="0"/>
         <v>1291</v>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="53">
         <f t="shared" si="0"/>
         <v>2338</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="52">
         <f t="shared" si="0"/>
         <v>32.18</v>
       </c>
-      <c r="I29" s="25" t="str">
+      <c r="I29" s="52" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J29" s="25" t="str">
+      <c r="J29" s="52" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A30" s="23" t="s">
+    <row r="30" s="1" customFormat="1" spans="1:10">
+      <c r="A30" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="25" t="str">
+      <c r="B30" s="51"/>
+      <c r="C30" s="52" t="str">
         <f t="shared" ref="C30:J30" si="1">IF(C9=" "," ",IF(C29=" "," ",AVERAGE(C9:C28)))</f>
         <v/>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="52">
         <f t="shared" si="1"/>
-        <v>87.945999999999998</v>
-      </c>
-      <c r="E30" s="25">
+        <v>87.946</v>
+      </c>
+      <c r="E30" s="52">
         <f t="shared" si="1"/>
-        <v>24.565999999999999</v>
-      </c>
-      <c r="F30" s="26">
+        <v>24.566</v>
+      </c>
+      <c r="F30" s="53">
         <f t="shared" si="1"/>
         <v>1313.2</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="53">
         <f t="shared" si="1"/>
         <v>2441</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="52">
         <f t="shared" si="1"/>
-        <v>33.921999999999997</v>
-      </c>
-      <c r="I30" s="25" t="str">
+        <v>33.922</v>
+      </c>
+      <c r="I30" s="52" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J30" s="25" t="str">
+      <c r="J30" s="52" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A31" s="23" t="s">
+    <row r="31" s="1" customFormat="1" spans="1:10">
+      <c r="A31" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25" t="str">
+      <c r="B31" s="51"/>
+      <c r="C31" s="52" t="str">
         <f t="shared" ref="C31:J31" si="2">IF(C9=" "," ",IF(C29=" "," ",MAX(C9:C28)))</f>
         <v/>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="52">
         <f t="shared" si="2"/>
         <v>89.42</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="52">
         <f t="shared" si="2"/>
         <v>27.49</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="53">
         <f t="shared" si="2"/>
         <v>1329</v>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="53">
         <f t="shared" si="2"/>
         <v>2580</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="52">
         <f t="shared" si="2"/>
         <v>34.64</v>
       </c>
-      <c r="I31" s="25" t="str">
+      <c r="I31" s="52" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J31" s="25" t="str">
+      <c r="J31" s="52" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A32" s="23" t="s">
+    <row r="32" s="1" customFormat="1" spans="1:10">
+      <c r="A32" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25" t="str">
+      <c r="B32" s="51"/>
+      <c r="C32" s="52" t="str">
         <f t="shared" ref="C32:J32" si="3">IF(C9=" "," ",IF(C29=" "," ",STDEV(C9:C28)))</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="52">
         <f t="shared" si="3"/>
-        <v>0.95096267014010705</v>
-      </c>
-      <c r="E32" s="25">
+        <v>0.950962670140107</v>
+      </c>
+      <c r="E32" s="52">
         <f t="shared" si="3"/>
         <v>1.65771831141482</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="52">
         <f t="shared" si="3"/>
         <v>15.626899884494</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="52">
         <f t="shared" si="3"/>
         <v>105.375518978556</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="52">
         <f t="shared" si="3"/>
         <v>1.01622832080197</v>
       </c>
-      <c r="I32" s="25" t="str">
+      <c r="I32" s="52" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J32" s="25" t="str">
+      <c r="J32" s="52" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A33" s="27" t="s">
+    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A33" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="40"/>
-    </row>
-    <row r="34" spans="1:10" s="1" customFormat="1" ht="16">
-      <c r="A34" s="32" t="s">
+      <c r="B33" s="55"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:10">
+      <c r="A34" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="33"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="C1:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I7:I8"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -2375,9 +2903,18 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F4:F6"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="C1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <headerFooter/>
 </worksheet>
 </file>